--- a/Development/유민규/Evaluation_DataSet_v3.xlsx
+++ b/Development/유민규/Evaluation_DataSet_v3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbdal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dbdal\Desktop\멋사 AI NLP\AI NLP05_6Team\project3\Development\유민규\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE12EBA2-E743-48F0-BD8E-830AC5327643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE42CE7F-2009-4B29-A863-671D5E72D2C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="평가데이터셋 V4_1" sheetId="2" r:id="rId1"/>
